--- a/sheets/대금율보/검수/폴로네이즈.xlsx
+++ b/sheets/대금율보/검수/폴로네이즈.xlsx
@@ -4632,7 +4632,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –潕</t>
         </is>
       </c>
@@ -4660,7 +4660,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –無</t>
         </is>
       </c>
@@ -4698,7 +4698,7 @@
       <c r="I4" s="26"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">南‹
+          <t xml:space="preserve">南
 無汰</t>
         </is>
       </c>
@@ -4722,7 +4722,7 @@
       <c r="C5" s="27"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶋‹
+          <t xml:space="preserve">㶋
 –淋湳</t>
         </is>
       </c>
@@ -4750,7 +4750,7 @@
       <c r="K5" s="28"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㽔‹
+          <t xml:space="preserve">㽔
 –林南</t>
         </is>
       </c>
@@ -4795,7 +4795,7 @@
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –無</t>
         </is>
       </c>
@@ -4893,14 +4893,14 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –潕</t>
         </is>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –潕</t>
         </is>
       </c>
@@ -4921,14 +4921,14 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –無</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –無</t>
         </is>
       </c>
@@ -4983,7 +4983,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶋‹
+          <t xml:space="preserve">㶋
 –淋湳</t>
         </is>
       </c>
@@ -5011,7 +5011,7 @@
       <c r="I11" s="27"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㽔‹
+          <t xml:space="preserve">㽔
 –林南</t>
         </is>
       </c>
@@ -5028,7 +5028,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –淋</t>
         </is>
       </c>
@@ -5056,7 +5056,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太‹
+          <t xml:space="preserve">太
 –林</t>
         </is>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –浹㶋</t>
         </is>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="I14" s="28"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太‹
+          <t xml:space="preserve">太
 –夾㽔</t>
         </is>
       </c>
@@ -5168,7 +5168,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹
+          <t xml:space="preserve">潕
 –汰</t>
         </is>
       </c>
@@ -5189,14 +5189,14 @@
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">夾‹
+          <t xml:space="preserve">夾
 –潢</t>
         </is>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –汰</t>
         </is>
       </c>
@@ -5258,7 +5258,7 @@
       <c r="C17" s="28"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 –潕潢</t>
         </is>
       </c>
@@ -5286,7 +5286,7 @@
       <c r="K17" s="28"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南‹
+          <t xml:space="preserve">南
 –無潢</t>
         </is>
       </c>
@@ -5303,7 +5303,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 –潢</t>
         </is>
       </c>
@@ -5391,7 +5391,7 @@
       <c r="C20" s="27"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –㶋</t>
         </is>
       </c>
@@ -5418,7 +5418,7 @@
       <c r="K20" s="27"/>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –㽔</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/폴로네이즈.xlsx
+++ b/sheets/대금율보/검수/폴로네이즈.xlsx
@@ -4585,24 +4585,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="19.86" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.86" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="19.86" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="19.86" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="19.86" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="19.86" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="73.57" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="73.57" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="73.57" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="73.57" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="73.57" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="73.57" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="M8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="73.57" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="73.57" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="73.57" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M11" s="28"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="73.57" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="M12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="73.57" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="M13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="73.57" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="M14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="73.57" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="73.57" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="73.57" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="M17" s="27"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="73.57" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="M18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="73.57" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="M19" s="25"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="73.57" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -5430,6 +5430,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
 </worksheet>
 </file>